--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484296_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484296_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1045</v>
+        <v>7.9565</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8541</v>
+        <v>8.087400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2504</v>
+        <v>-0.1309</v>
       </c>
       <c r="G2" t="n">
         <v>2.2417</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4721</v>
+        <v>1.3241</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7784</v>
+        <v>0.4549</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2505</v>
+        <v>0.8692</v>
       </c>
       <c r="V2" t="n">
         <v>2.4373</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6207</v>
+        <v>6.2611</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4949</v>
+        <v>5.3532</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1258</v>
+        <v>0.9079</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0387</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1989</v>
+        <v>1.8393</v>
       </c>
       <c r="T3" t="n">
-        <v>1.175</v>
+        <v>1.0333</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0239</v>
+        <v>0.806</v>
       </c>
       <c r="V3" t="n">
         <v>4.8745</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8489</v>
+        <v>2.3676</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6034</v>
+        <v>1.8469</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2455</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.317</v>
+        <v>-1.0831</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6956</v>
+        <v>0.0494</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6214</v>
+        <v>-1.1324</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9453</v>
+        <v>1.4442</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6216</v>
+        <v>0.8224</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3237</v>
+        <v>0.6218</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2623</v>
+        <v>-2.5273</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3172</v>
+        <v>-0.7731</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-1.7542</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8105</v>
+        <v>1.646</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4477</v>
+        <v>0.8249</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3628</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6642</v>
+        <v>0.5545</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3869</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.284</v>
+        <v>-0.0135</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2808</v>
+        <v>-1.0956</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0033</v>
+        <v>1.0821</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0831</v>
+        <v>-1.317</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0494</v>
+        <v>-0.6956</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1324</v>
+        <v>-0.6214</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4442</v>
+        <v>0.9453</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8224</v>
+        <v>0.6216</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6218</v>
+        <v>0.3237</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5273</v>
+        <v>-2.2623</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7731</v>
+        <v>-1.3172</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7542</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5624</v>
+        <v>2.9481</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2588</v>
+        <v>1.7487</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3037</v>
+        <v>1.1994</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5545</v>
+        <v>-0.6642</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6642</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4315</v>
+        <v>-0.8395</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2928</v>
+        <v>-0.8137</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8613</v>
+        <v>-0.0258</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.7135</v>
+        <v>-1.2068</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5396</v>
+        <v>-0.3973</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1739</v>
+        <v>-0.8095</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.694</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.7345</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0194</v>
+        <v>-0.6146</v>
       </c>
       <c r="N6" t="n">
         <v>0.1949</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2144</v>
+        <v>-0.8095</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6726</v>
+        <v>-0.2187</v>
       </c>
       <c r="T6" t="n">
-        <v>1.296</v>
+        <v>-0.2214</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3766</v>
+        <v>0.0027</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2051</v>
+        <v>-1.1226</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0159</v>
+        <v>-1.6393</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1892</v>
+        <v>0.5167</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2068</v>
+        <v>-2.2321</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3973</v>
+        <v>-1.0197</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8095</v>
+        <v>-1.2124</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-1.3382</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.5308</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.8073</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6146</v>
+        <v>-0.8939</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1949</v>
+        <v>-0.4889</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8095</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5844</v>
+        <v>0.996</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4237</v>
+        <v>0.6756</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1607</v>
+        <v>0.3205</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.926</v>
+        <v>-1.9892</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3065</v>
+        <v>-2.1424</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3805</v>
+        <v>0.1532</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2321</v>
+        <v>-2.7135</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0197</v>
+        <v>-1.5396</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2124</v>
+        <v>-1.1739</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3382</v>
+        <v>-1.694</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5308</v>
+        <v>-1.7345</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8073</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8939</v>
+        <v>-1.0194</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4889</v>
+        <v>0.1949</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>-1.2144</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1926</v>
+        <v>1.115</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0083</v>
+        <v>0.4465</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1843</v>
+        <v>0.6685</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
         <v>-0.2772</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.332</v>
+        <v>-2.1196</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2461</v>
+        <v>-0.3878</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0858</v>
+        <v>-1.7318</v>
       </c>
       <c r="G9" t="n">
         <v>-1.432</v>
@@ -1156,13 +1156,13 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.514</v>
+        <v>0.7264</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3798</v>
+        <v>0.2381</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1342</v>
+        <v>0.4883</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7547</v>
+        <v>-3.6868</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8792</v>
+        <v>-2.1108</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8756</v>
+        <v>-1.576</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9585</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7962</v>
+        <v>0.2717</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.0421</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0699</v>
+        <v>0.2297</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8279</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.2088</v>
+        <v>6.814</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4927</v>
+        <v>7.097900000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2837999999999998</v>
+        <v>-0.2838999999999996</v>
       </c>
       <c r="G11" t="n">
         <v>-9.740000000000002</v>
@@ -1312,13 +1312,13 @@
         <v>11.7205</v>
       </c>
       <c r="S11" t="n">
-        <v>10.0425</v>
+        <v>10.6479</v>
       </c>
       <c r="T11" t="n">
-        <v>4.6372</v>
+        <v>5.242699999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>5.4054</v>
+        <v>5.405400000000001</v>
       </c>
       <c r="V11" t="n">
         <v>4.929499999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2701</v>
+        <v>3.7217</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7094</v>
+        <v>2.406</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5608</v>
+        <v>1.3157</v>
       </c>
       <c r="G12" t="n">
         <v>3.8806</v>
@@ -1390,13 +1390,13 @@
         <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4414</v>
+        <v>-0.9899</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3272</v>
+        <v>-0.6306</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1142</v>
+        <v>-0.3593</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7318</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.663</v>
+        <v>1.5037</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3561</v>
+        <v>1.9517</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6931</v>
+        <v>-0.448</v>
       </c>
       <c r="G13" t="n">
         <v>1.5409</v>
@@ -1468,13 +1468,13 @@
         <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4556</v>
+        <v>-0.6149</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0384</v>
+        <v>-0.4429</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4172</v>
+        <v>-0.1721</v>
       </c>
       <c r="V13" t="n">
         <v>1.1638</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4503</v>
+        <v>0.7887</v>
       </c>
       <c r="E14" t="n">
-        <v>1.235</v>
+        <v>1.4373</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7847</v>
+        <v>-0.6485</v>
       </c>
       <c r="G14" t="n">
         <v>0.467</v>
@@ -1546,13 +1546,13 @@
         <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.472</v>
+        <v>-1.1336</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.6451</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6246</v>
+        <v>-0.4885</v>
       </c>
       <c r="V14" t="n">
         <v>1.6506</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5208</v>
+        <v>-0.2835</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3751</v>
+        <v>1.4763</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8959</v>
+        <v>-1.7597</v>
       </c>
       <c r="G15" t="n">
         <v>4.2012</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0112</v>
+        <v>-1.7739</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8803</v>
+        <v>-0.7792</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1309</v>
+        <v>-0.9948</v>
       </c>
       <c r="V15" t="n">
         <v>-3.1014</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6724</v>
+        <v>-0.4429</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4265</v>
+        <v>0.6287</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0989</v>
+        <v>-1.0716</v>
       </c>
       <c r="G16" t="n">
         <v>0.1571</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.242</v>
+        <v>-1.0125</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7125</v>
+        <v>-0.5103</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5295</v>
+        <v>-0.5022</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5642</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7486</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6774</v>
+        <v>0.1681</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9288</v>
+        <v>-0.8884</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8472</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5652</v>
+        <v>1.5925</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2821</v>
+        <v>-0.6475</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6778</v>
+        <v>1.4398</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3945</v>
+        <v>1.4121</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2833</v>
+        <v>0.0276</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1695</v>
+        <v>-0.4947</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1707</v>
+        <v>0.1804</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0012</v>
+        <v>-0.6751</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-1.1109</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4483</v>
+        <v>-0.295</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4443</v>
+        <v>-0.8159</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5545</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9031</v>
+        <v>-1.196</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0669</v>
+        <v>-1.8796</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9701</v>
+        <v>0.6837</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9451000000000001</v>
+        <v>2.8472</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5925</v>
+        <v>2.5652</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6475</v>
+        <v>0.2821</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4398</v>
+        <v>2.6778</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4121</v>
+        <v>2.3945</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0276</v>
+        <v>0.2833</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4947</v>
+        <v>0.1695</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1804</v>
+        <v>0.1707</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6751</v>
+        <v>-0.0012</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2937</v>
+        <v>-1.34</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3961</v>
+        <v>-0.6505</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8976</v>
+        <v>-0.6894</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5545</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8489</v>
+        <v>-1.8216</v>
       </c>
       <c r="E19" t="n">
         <v>-1.2654</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5835</v>
+        <v>-0.5562</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9297</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6284</v>
+        <v>-0.6012</v>
       </c>
       <c r="T19" t="n">
         <v>-0.6052</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0232</v>
+        <v>0.0041</v>
       </c>
       <c r="V19" t="n">
         <v>0.0999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9363</v>
+        <v>-3.0064</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6383</v>
+        <v>-2.436</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.298</v>
+        <v>-0.5704</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9502</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5668</v>
+        <v>-0.637</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.6451</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2805</v>
+        <v>0.0081</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3959</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9621</v>
+        <v>-4.7521</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3042</v>
+        <v>-2.2031</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.658</v>
+        <v>-2.549</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4191</v>
@@ -2092,13 +2092,13 @@
         <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0389</v>
+        <v>-0.8289</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3026</v>
+        <v>-0.2015</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7363</v>
+        <v>-0.6274</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9414</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2088</v>
+        <v>-6.2087</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2837000000000005</v>
+        <v>0.2839999999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.492599999999999</v>
+        <v>-6.4924</v>
       </c>
       <c r="G22" t="n">
         <v>9.7401</v>
@@ -2161,7 +2161,7 @@
         <v>-2.7043</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>-0.9766999999999998</v>
       </c>
       <c r="Q22" t="n">
         <v>-11.7205</v>
@@ -2170,13 +2170,13 @@
         <v>10.7438</v>
       </c>
       <c r="S22" t="n">
-        <v>-10.0426</v>
+        <v>-10.0428</v>
       </c>
       <c r="T22" t="n">
-        <v>-5.4052</v>
+        <v>-5.4054</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.6373</v>
+        <v>-4.6374</v>
       </c>
       <c r="V22" t="n">
         <v>-4.9294</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484296_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484296_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0135</v>
+        <v>1.521</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0956</v>
+        <v>1.521</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0821</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.317</v>
+        <v>1.521</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6956</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6214</v>
+        <v>1.214</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9453</v>
+        <v>1.521</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6216</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3237</v>
+        <v>1.214</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2623</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3172</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9451000000000001</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9481</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7487</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1994</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8395</v>
+        <v>-0.0135</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8137</v>
+        <v>-1.0956</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0258</v>
+        <v>1.0821</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2068</v>
+        <v>-1.317</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3973</v>
+        <v>-0.6956</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8095</v>
+        <v>-0.6214</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.9453</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.6216</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.3237</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6146</v>
+        <v>-2.2623</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1949</v>
+        <v>-1.3172</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8095</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2187</v>
+        <v>2.9481</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2214</v>
+        <v>1.7487</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0027</v>
+        <v>1.1994</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1226</v>
+        <v>-0.8395</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6393</v>
+        <v>-0.8137</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5167</v>
+        <v>-0.0258</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2321</v>
+        <v>-1.2068</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0197</v>
+        <v>-0.3973</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2124</v>
+        <v>-0.8095</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3382</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5308</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8073</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8939</v>
+        <v>-0.6146</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4889</v>
+        <v>0.1949</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4051</v>
+        <v>-0.8095</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>0.996</v>
+        <v>-0.2187</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6756</v>
+        <v>-0.2214</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3205</v>
+        <v>0.0027</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9892</v>
+        <v>-1.1226</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1424</v>
+        <v>-1.6393</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1532</v>
+        <v>0.5167</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7135</v>
+        <v>-2.2321</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5396</v>
+        <v>-1.0197</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1739</v>
+        <v>-1.2124</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.694</v>
+        <v>-1.3382</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7345</v>
+        <v>-0.5308</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>-0.8073</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0194</v>
+        <v>-0.8939</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1949</v>
+        <v>-0.4889</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2144</v>
+        <v>-0.4051</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>1.115</v>
+        <v>0.996</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4465</v>
+        <v>0.6756</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6685</v>
+        <v>0.3205</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1196</v>
+        <v>-1.9892</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3878</v>
+        <v>-2.1424</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7318</v>
+        <v>0.1532</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.432</v>
+        <v>-2.7135</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4134</v>
+        <v>-1.5396</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8454</v>
+        <v>-1.1739</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5461</v>
+        <v>-1.694</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9071</v>
+        <v>-1.7345</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.361</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9781</v>
+        <v>-1.0194</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4937</v>
+        <v>0.1949</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4844</v>
+        <v>-1.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7264</v>
+        <v>1.115</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2381</v>
+        <v>0.4465</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4883</v>
+        <v>0.6685</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6868</v>
+        <v>-3.6406</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1108</v>
+        <v>-1.9088</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.576</v>
+        <v>-1.7318</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9585</v>
+        <v>-2.953</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5902</v>
+        <v>1.1064</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5487</v>
+        <v>-4.0594</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0041</v>
+        <v>-0.9749</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3303</v>
+        <v>1.6001</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3344</v>
+        <v>-2.575</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9544</v>
+        <v>-1.9781</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2599</v>
+        <v>-0.4937</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2144</v>
+        <v>-1.4844</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.1721</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-2.1488</v>
       </c>
       <c r="R10" t="n">
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2717</v>
+        <v>0.7264</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0421</v>
+        <v>0.2381</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2297</v>
+        <v>0.4883</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.814</v>
+        <v>-3.6868</v>
       </c>
       <c r="E11" t="n">
-        <v>7.097900000000001</v>
+        <v>-2.1108</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2838999999999996</v>
+        <v>-1.576</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.740000000000002</v>
+        <v>-0.9585</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9971</v>
+        <v>1.5902</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.742900000000001</v>
+        <v>-2.5487</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6202</v>
+        <v>-0.0041</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9159</v>
+        <v>1.3303</v>
       </c>
       <c r="L11" t="n">
-        <v>2.7043</v>
+        <v>-1.3344</v>
       </c>
       <c r="M11" t="n">
-        <v>-14.3601</v>
+        <v>-0.9544</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.9131</v>
+        <v>0.2599</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.447299999999998</v>
+        <v>-1.2144</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9765999999999999</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.7439</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>11.7205</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>10.6479</v>
+        <v>0.2717</v>
       </c>
       <c r="T11" t="n">
-        <v>5.242699999999999</v>
+        <v>0.0421</v>
       </c>
       <c r="U11" t="n">
-        <v>5.405400000000001</v>
+        <v>0.2297</v>
       </c>
       <c r="V11" t="n">
-        <v>4.929499999999999</v>
+        <v>-1.8279</v>
       </c>
       <c r="W11" t="n">
-        <v>7.978899999999999</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0494</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7217</v>
+        <v>6.814000000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>2.406</v>
+        <v>7.097900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3157</v>
+        <v>-0.2838999999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8806</v>
+        <v>-9.74</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6646</v>
+        <v>-2.997100000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5452</v>
+        <v>-6.742900000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0366</v>
+        <v>4.6202</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8353</v>
+        <v>1.9159</v>
       </c>
       <c r="L12" t="n">
-        <v>3.8719</v>
+        <v>2.704299999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.844</v>
+        <v>-14.3601</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1707</v>
+        <v>-4.9131</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6733</v>
+        <v>-9.4473</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5627</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-10.7439</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5627</v>
+        <v>11.7205</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9899</v>
+        <v>10.6479</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6306</v>
+        <v>5.2427</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3593</v>
+        <v>5.4054</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7318</v>
+        <v>4.929500000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>7.978899999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7318</v>
-      </c>
+        <v>-3.0494</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5037</v>
+        <v>3.7217</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9517</v>
+        <v>2.406</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.448</v>
+        <v>1.3157</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5409</v>
+        <v>3.8806</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2264</v>
+        <v>-0.6646</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7673</v>
+        <v>4.5452</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9655</v>
+        <v>3.0366</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06270000000000001</v>
+        <v>-0.8353</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9029</v>
+        <v>3.8719</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4247</v>
+        <v>0.844</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2891</v>
+        <v>0.1707</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1356</v>
+        <v>0.6733</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6149</v>
+        <v>-0.9899</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4429</v>
+        <v>-0.6306</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1721</v>
+        <v>-0.3593</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1638</v>
+        <v>-0.7318</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
+        <v>-0.7318</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7887</v>
+        <v>1.5037</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4373</v>
+        <v>1.9517</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6485</v>
+        <v>-0.448</v>
       </c>
       <c r="G14" t="n">
-        <v>0.467</v>
+        <v>1.5409</v>
       </c>
       <c r="H14" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.2264</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4585</v>
+        <v>1.7673</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2311</v>
+        <v>1.9655</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0371</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2683</v>
+        <v>1.9029</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7641</v>
+        <v>-0.4247</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0456</v>
+        <v>-0.2891</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8097</v>
+        <v>-0.1356</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1336</v>
+        <v>-0.6149</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6451</v>
+        <v>-0.4429</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4885</v>
+        <v>-0.1721</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6506</v>
+        <v>1.1638</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8279</v>
+        <v>2.3824</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1773</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2835</v>
+        <v>0.7887</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4763</v>
+        <v>1.4373</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7597</v>
+        <v>-0.6485</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2012</v>
+        <v>0.467</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5577</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6435</v>
+        <v>0.4585</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8963</v>
+        <v>1.2311</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9263</v>
+        <v>-0.0371</v>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>1.2683</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3049</v>
+        <v>-0.7641</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3686</v>
+        <v>0.0456</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6735</v>
+        <v>-0.8097</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7739</v>
+        <v>-1.1336</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7792</v>
+        <v>-0.6451</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9948</v>
+        <v>-0.4885</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.1014</v>
+        <v>1.6506</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6642</v>
+        <v>1.8279</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4373</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4429</v>
+        <v>-0.2835</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6287</v>
+        <v>1.4763</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0716</v>
+        <v>-1.7597</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1571</v>
+        <v>4.2012</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3845</v>
+        <v>1.5577</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2274</v>
+        <v>2.6435</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5259</v>
+        <v>3.8963</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5387</v>
+        <v>1.9263</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0128</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3688</v>
+        <v>0.3049</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1542</v>
+        <v>-0.3686</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2146</v>
+        <v>0.6735</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0125</v>
+        <v>-1.7739</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5103</v>
+        <v>-0.7792</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5022</v>
+        <v>-0.9948</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5642</v>
+        <v>-3.1014</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3869</v>
+        <v>-0.6642</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1773</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.4429</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1681</v>
+        <v>0.6287</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8884</v>
+        <v>-1.0716</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.1571</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5925</v>
+        <v>1.3845</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6475</v>
+        <v>-1.2274</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4398</v>
+        <v>1.5259</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4121</v>
+        <v>1.5387</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0276</v>
+        <v>-0.0128</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4947</v>
+        <v>-1.3688</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1804</v>
+        <v>-0.1542</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6751</v>
+        <v>-1.2146</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1109</v>
+        <v>-1.0125</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.295</v>
+        <v>-0.5103</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8159</v>
+        <v>-0.5022</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5545</v>
+        <v>-0.5642</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5545</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.196</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8796</v>
+        <v>0.1681</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6837</v>
+        <v>-0.8884</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8472</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5652</v>
+        <v>1.5925</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2821</v>
+        <v>-0.6475</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6778</v>
+        <v>1.4398</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3945</v>
+        <v>1.4121</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2833</v>
+        <v>0.0276</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1695</v>
+        <v>-0.4947</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1707</v>
+        <v>0.1804</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0012</v>
+        <v>-0.6751</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.34</v>
+        <v>-1.1109</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6505</v>
+        <v>-0.295</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6894</v>
+        <v>-0.8159</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5545</v>
@@ -1874,12 +1955,17 @@
       </c>
       <c r="X18" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8216</v>
+        <v>-1.196</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2654</v>
+        <v>-1.8796</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5562</v>
+        <v>0.6837</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9297</v>
+        <v>2.8472</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1857</v>
+        <v>2.5652</v>
       </c>
       <c r="I19" t="n">
-        <v>0.256</v>
+        <v>0.2821</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7035</v>
+        <v>2.6778</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6319</v>
+        <v>2.3945</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3354</v>
+        <v>0.2833</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6332</v>
+        <v>0.1695</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5538</v>
+        <v>0.1707</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0793</v>
+        <v>-0.0012</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6012</v>
+        <v>-1.34</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6052</v>
+        <v>-0.6505</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0041</v>
+        <v>-0.6894</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0999</v>
+        <v>-0.5545</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4869</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0064</v>
+        <v>-1.8216</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.436</v>
+        <v>-1.2654</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5704</v>
+        <v>-0.5562</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9502</v>
+        <v>-0.9297</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0586</v>
+        <v>-1.1857</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1084</v>
+        <v>0.256</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7909</v>
+        <v>0.7035</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2254</v>
+        <v>-0.6319</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5655</v>
+        <v>1.3354</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1593</v>
+        <v>-1.6332</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.5538</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6739000000000001</v>
+        <v>-1.0793</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.637</v>
+        <v>-0.6012</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6451</v>
+        <v>-0.6052</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0081</v>
+        <v>0.0041</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3959</v>
+        <v>0.0999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3959</v>
+        <v>0.4869</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7521</v>
+        <v>-3.0064</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2031</v>
+        <v>-2.436</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.549</v>
+        <v>-0.5704</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4191</v>
+        <v>-1.9502</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0241</v>
+        <v>-2.0586</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4431</v>
+        <v>0.1084</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3254</v>
+        <v>-1.7909</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3083</v>
+        <v>-1.2254</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.5655</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0937</v>
+        <v>-0.1593</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2842</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8095</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8289</v>
+        <v>-0.637</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2015</v>
+        <v>-0.6451</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6274</v>
+        <v>0.0081</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9414</v>
+        <v>-1.3959</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-1.3959</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,152 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-4.7521</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2.2031</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-2.549</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.4191</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.4431</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.3254</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.0937</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.2842</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.8095</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.8289</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.2015</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.6274</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.9414</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484296_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>-6.2087</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>0.2839999999999998</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>-6.4924</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>9.7401</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>2.997100000000001</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>6.742999999999999</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>14.3602</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>4.9129</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>9.4475</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>-4.6201</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>-1.9157</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>-2.7043</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>-0.9766999999999998</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>-11.7205</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>10.7438</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>-10.0428</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>-5.4054</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>-4.6374</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V23" t="n">
         <v>-4.9294</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W23" t="n">
         <v>3.0495</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X23" t="n">
         <v>-7.978900000000001</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
